--- a/docs/SnugTalk-Test-Cases.xlsx
+++ b/docs/SnugTalk-Test-Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asads\AppData\Local\Temp\claude\C--Users-asads-Videos-SnugTalk\b33e872c-356d-436e-a017-77a46f812986\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3ED4C00-5055-4566-A68D-26069FEFCC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88796D0-F3E3-42E4-A534-A0549DE48302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$K$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$K$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="734">
   <si>
     <t>SnugTalk - how to use this sheet</t>
   </si>
@@ -1781,6 +1781,183 @@
   </si>
   <si>
     <t>All content reachable on every page. Nothing clipped.</t>
+  </si>
+  <si>
+    <t>B-01</t>
+  </si>
+  <si>
+    <t>Blocking</t>
+  </si>
+  <si>
+    <t>Admin can block a user</t>
+  </si>
+  <si>
+    <t>Signed in as admin; a test member exists</t>
+  </si>
+  <si>
+    <t>Users &gt; row menu on the test member &gt; Block. Read the dialog, confirm.</t>
+  </si>
+  <si>
+    <t>Confirmation explains nothing is deleted. After confirming, the row shows a red 'Blocked' badge and is dimmed.</t>
+  </si>
+  <si>
+    <t>B-02</t>
+  </si>
+  <si>
+    <t>Blocked user cannot sign in</t>
+  </si>
+  <si>
+    <t>A member was just blocked</t>
+  </si>
+  <si>
+    <t>Sign out. Try to sign in as that member with the CORRECT password.</t>
+  </si>
+  <si>
+    <t>Refused. A standing red notice reads 'This account is blocked' and tells them to contact the administrator. It does not disappear on its own.</t>
+  </si>
+  <si>
+    <t>B-03</t>
+  </si>
+  <si>
+    <t>Blocked user cannot use Google</t>
+  </si>
+  <si>
+    <t>The blocked member signed up with Google</t>
+  </si>
+  <si>
+    <t>On /sign-in click 'Continue with Google' and complete it.</t>
+  </si>
+  <si>
+    <t>Sent back to sign-in with the blocked message. NOT signed in. Google is not a way around the block.</t>
+  </si>
+  <si>
+    <t>B-04</t>
+  </si>
+  <si>
+    <t>Existing session stops working</t>
+  </si>
+  <si>
+    <t>Blocked member is ALREADY signed in in another browser</t>
+  </si>
+  <si>
+    <t>In that other browser, refresh or click any dashboard link.</t>
+  </si>
+  <si>
+    <t>Kicked out. Cannot keep using the site on the old session.</t>
+  </si>
+  <si>
+    <t>B-05</t>
+  </si>
+  <si>
+    <t>Wrong password on a blocked account</t>
+  </si>
+  <si>
+    <t>Account is blocked</t>
+  </si>
+  <si>
+    <t>Try to sign in with the WRONG password.</t>
+  </si>
+  <si>
+    <t>Says the email or password is incorrect - the SAME as any other wrong password. It must NOT reveal that the account is blocked.</t>
+  </si>
+  <si>
+    <t>B-06</t>
+  </si>
+  <si>
+    <t>Admin can unblock</t>
+  </si>
+  <si>
+    <t>A blocked member exists</t>
+  </si>
+  <si>
+    <t>Users &gt; row menu &gt; Unblock. Confirm.</t>
+  </si>
+  <si>
+    <t>Badge disappears. The member can sign in again immediately with their existing password.</t>
+  </si>
+  <si>
+    <t>B-07</t>
+  </si>
+  <si>
+    <t>Blocking keeps their data</t>
+  </si>
+  <si>
+    <t>A member with messages and a meeting request</t>
+  </si>
+  <si>
+    <t>Block them, then unblock them, then sign in as them.</t>
+  </si>
+  <si>
+    <t>Their conversations, messages and meeting requests are all still there, unchanged.</t>
+  </si>
+  <si>
+    <t>B-08</t>
+  </si>
+  <si>
+    <t>Admin cannot block themselves</t>
+  </si>
+  <si>
+    <t>Open the row menu on your OWN row.</t>
+  </si>
+  <si>
+    <t>Block is disabled. If forced, the server refuses with a clear message.</t>
+  </si>
+  <si>
+    <t>B-09</t>
+  </si>
+  <si>
+    <t>Cannot block the last admin</t>
+  </si>
+  <si>
+    <t>Only one unblocked admin exists</t>
+  </si>
+  <si>
+    <t>As that admin, try to block the only other admin, or have a second admin try to block the last one.</t>
+  </si>
+  <si>
+    <t>Refused with a message about always needing one unblocked admin.</t>
+  </si>
+  <si>
+    <t>B-10</t>
+  </si>
+  <si>
+    <t>Cannot impersonate a blocked user</t>
+  </si>
+  <si>
+    <t>Open the row menu on the blocked member.</t>
+  </si>
+  <si>
+    <t>'View as this user' is disabled. If forced, the server refuses and says to unblock first.</t>
+  </si>
+  <si>
+    <t>B-11</t>
+  </si>
+  <si>
+    <t>Blocked users are visible at a glance</t>
+  </si>
+  <si>
+    <t>At least one blocked user</t>
+  </si>
+  <si>
+    <t>Look down the Users list.</t>
+  </si>
+  <si>
+    <t>Blocked rows are clearly marked with a red badge and dimmed, distinct from 'Unverified'.</t>
+  </si>
+  <si>
+    <t>B-12</t>
+  </si>
+  <si>
+    <t>Blocked user cannot use password reset to get in</t>
+  </si>
+  <si>
+    <t>A blocked account exists</t>
+  </si>
+  <si>
+    <t>Request a password reset for the blocked account and complete it with the emailed code.</t>
+  </si>
+  <si>
+    <t>The password may change, but signing in still shows the blocked notice.</t>
   </si>
   <si>
     <t>LAF-01</t>
@@ -2723,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -5941,46 +6118,46 @@
         <v>582</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>583</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>235</v>
+        <v>584</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H119" s="10"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
       <c r="K119" s="9"/>
     </row>
-    <row r="120" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>512</v>
+        <v>589</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H120" s="10"/>
       <c r="I120" s="7"/>
@@ -5989,133 +6166,133 @@
     </row>
     <row r="121" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>46</v>
+        <v>594</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="H121" s="10"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
       <c r="K121" s="9"/>
     </row>
-    <row r="122" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>46</v>
+        <v>599</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H122" s="10"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7"/>
       <c r="K122" s="9"/>
     </row>
-    <row r="123" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>235</v>
+        <v>604</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="H123" s="10"/>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
       <c r="K123" s="9"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>115</v>
+        <v>609</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="H124" s="10"/>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
       <c r="K124" s="9"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>46</v>
+        <v>614</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="H125" s="10"/>
       <c r="I125" s="7"/>
@@ -6124,25 +6301,25 @@
     </row>
     <row r="126" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>613</v>
+        <v>146</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="H126" s="10"/>
       <c r="I126" s="7"/>
@@ -6151,79 +6328,79 @@
     </row>
     <row r="127" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="H127" s="10"/>
       <c r="I127" s="7"/>
       <c r="J127" s="7"/>
       <c r="K127" s="9"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H128" s="10"/>
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
       <c r="K128" s="9"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="H129" s="10"/>
       <c r="I129" s="7"/>
@@ -6232,25 +6409,25 @@
     </row>
     <row r="130" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>631</v>
+        <v>582</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>46</v>
+        <v>637</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="H130" s="10"/>
       <c r="I130" s="7"/>
@@ -6259,25 +6436,25 @@
     </row>
     <row r="131" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="H131" s="10"/>
       <c r="I131" s="7"/>
@@ -6286,25 +6463,25 @@
     </row>
     <row r="132" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="H132" s="10"/>
       <c r="I132" s="7"/>
@@ -6313,25 +6490,25 @@
     </row>
     <row r="133" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>235</v>
+        <v>46</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H133" s="10"/>
       <c r="I133" s="7"/>
@@ -6340,39 +6517,363 @@
     </row>
     <row r="134" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>235</v>
+        <v>46</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="H134" s="10"/>
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
       <c r="K134" s="9"/>
     </row>
+    <row r="135" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A135" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="H135" s="10"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="7"/>
+      <c r="K135" s="9"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A136" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="H136" s="10"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="7"/>
+      <c r="K136" s="9"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A137" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="H137" s="10"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
+      <c r="K137" s="9"/>
+    </row>
+    <row r="138" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A138" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="H138" s="10"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="9"/>
+    </row>
+    <row r="139" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A139" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="H139" s="10"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="7"/>
+      <c r="K139" s="9"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A140" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="H140" s="10"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="7"/>
+      <c r="K140" s="9"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A141" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="H141" s="10"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="9"/>
+    </row>
+    <row r="142" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A142" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="H142" s="10"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
+      <c r="K142" s="9"/>
+    </row>
+    <row r="143" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A143" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="H143" s="10"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="7"/>
+      <c r="K143" s="9"/>
+    </row>
+    <row r="144" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A144" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="H144" s="10"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="7"/>
+      <c r="K144" s="9"/>
+    </row>
+    <row r="145" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A145" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="H145" s="10"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="7"/>
+      <c r="K145" s="9"/>
+    </row>
+    <row r="146" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+      <c r="A146" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="H146" s="10"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
+      <c r="K146" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K134" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="C2:C134">
+  <autoFilter ref="A1:K146" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="C2:C146">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H134">
+  <conditionalFormatting sqref="H2:H146">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6387,7 +6888,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, Blocked or N/A." promptTitle="Result" prompt="Mark the outcome of this test." sqref="H2:H134" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, Blocked or N/A." promptTitle="Result" prompt="Mark the outcome of this test." sqref="H2:H146" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6397,7 +6898,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6406,97 +6907,97 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>711</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="B3" s="12"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>654</v>
+        <v>713</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>655</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>656</v>
+        <v>715</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>657</v>
+        <v>716</v>
       </c>
       <c r="B6" s="12"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>658</v>
+        <v>717</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>659</v>
+        <v>718</v>
       </c>
       <c r="B9" s="11">
-        <f>COUNTA('Test Cases'!A2:A134)</f>
-        <v>133</v>
+        <f>COUNTA('Test Cases'!A2:A146)</f>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>660</v>
+        <v>719</v>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIF('Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIF('Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>661</v>
+        <v>720</v>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIF('Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIF('Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>662</v>
+        <v>721</v>
       </c>
       <c r="B12" s="11">
-        <f>COUNTIF('Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIF('Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>663</v>
+        <v>722</v>
       </c>
       <c r="B13" s="11">
-        <f>COUNTIF('Test Cases'!H2:H134,"N/A")</f>
+        <f>COUNTIF('Test Cases'!H2:H146,"N/A")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="B14" s="11">
         <f>B9-B10-B11-B12-B13</f>
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="B15" s="15">
         <f>IFERROR(B10/(B10+B11),0)</f>
@@ -6505,39 +7006,39 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>666</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B18" s="11">
-        <f>COUNTIF('Test Cases'!C2:C134,"High")</f>
-        <v>82</v>
+        <f>COUNTIF('Test Cases'!C2:C146,"High")</f>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
       <c r="B19" s="11">
-        <f>COUNTIFS('Test Cases'!C2:C134,"High",'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!C2:C146,"High",'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>669</v>
+        <v>728</v>
       </c>
       <c r="B20" s="11">
-        <f>COUNTIFS('Test Cases'!C2:C134,"High",'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!C2:C146,"High",'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -6545,19 +7046,19 @@
         <v>33</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>673</v>
+        <v>732</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>662</v>
+        <v>721</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>674</v>
+        <v>733</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -6565,23 +7066,23 @@
         <v>43</v>
       </c>
       <c r="B24" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A24)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A24)</f>
         <v>18</v>
       </c>
       <c r="C24" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A24,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A24,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D24" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A24,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A24,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E24" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A24,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A24,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F24" s="17">
-        <f t="shared" ref="F24:F37" si="0">B24-C24-D24-E24</f>
+        <f t="shared" ref="F24:F38" si="0">B24-C24-D24-E24</f>
         <v>18</v>
       </c>
     </row>
@@ -6590,19 +7091,19 @@
         <v>124</v>
       </c>
       <c r="B25" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A25)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A25)</f>
         <v>7</v>
       </c>
       <c r="C25" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A25,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A25,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D25" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A25,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A25,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E25" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A25,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A25,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F25" s="17">
@@ -6615,19 +7116,19 @@
         <v>154</v>
       </c>
       <c r="B26" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A26)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A26)</f>
         <v>11</v>
       </c>
       <c r="C26" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A26,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A26,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D26" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A26,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A26,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E26" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A26,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A26,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F26" s="17">
@@ -6640,19 +7141,19 @@
         <v>205</v>
       </c>
       <c r="B27" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A27)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A27)</f>
         <v>10</v>
       </c>
       <c r="C27" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A27,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A27,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D27" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A27,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A27,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E27" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A27,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A27,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F27" s="17">
@@ -6665,19 +7166,19 @@
         <v>251</v>
       </c>
       <c r="B28" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A28)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A28)</f>
         <v>11</v>
       </c>
       <c r="C28" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A28,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A28,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D28" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A28,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A28,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E28" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A28,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A28,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F28" s="17">
@@ -6690,19 +7191,19 @@
         <v>301</v>
       </c>
       <c r="B29" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A29)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A29)</f>
         <v>9</v>
       </c>
       <c r="C29" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A29,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A29,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D29" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A29,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A29,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E29" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A29,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A29,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F29" s="17">
@@ -6715,19 +7216,19 @@
         <v>343</v>
       </c>
       <c r="B30" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A30)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A30)</f>
         <v>8</v>
       </c>
       <c r="C30" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A30,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A30,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D30" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A30,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A30,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E30" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A30,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A30,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F30" s="17">
@@ -6740,19 +7241,19 @@
         <v>379</v>
       </c>
       <c r="B31" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A31)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A31)</f>
         <v>10</v>
       </c>
       <c r="C31" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A31,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A31,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D31" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A31,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A31,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E31" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A31,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A31,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F31" s="17">
@@ -6765,19 +7266,19 @@
         <v>425</v>
       </c>
       <c r="B32" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A32)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A32)</f>
         <v>6</v>
       </c>
       <c r="C32" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A32,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A32,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D32" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A32,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A32,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E32" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A32,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A32,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F32" s="17">
@@ -6790,19 +7291,19 @@
         <v>455</v>
       </c>
       <c r="B33" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A33)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A33)</f>
         <v>12</v>
       </c>
       <c r="C33" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A33,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A33,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D33" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A33,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A33,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E33" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A33,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A33,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F33" s="17">
@@ -6815,19 +7316,19 @@
         <v>510</v>
       </c>
       <c r="B34" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A34)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A34)</f>
         <v>15</v>
       </c>
       <c r="C34" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A34,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A34,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D34" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A34,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A34,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E34" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A34,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A34,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F34" s="17">
@@ -6840,72 +7341,97 @@
         <v>582</v>
       </c>
       <c r="B35" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A35)</f>
-        <v>7</v>
+        <f>COUNTIF('Test Cases'!B2:B146,A35)</f>
+        <v>12</v>
       </c>
       <c r="C35" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A35,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A35,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D35" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A35,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A35,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E35" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A35,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A35,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F35" s="17">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="B36" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A36)</f>
-        <v>4</v>
+        <f>COUNTIF('Test Cases'!B2:B146,A36)</f>
+        <v>7</v>
       </c>
       <c r="C36" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A36,'Test Cases'!H2:H134,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A36,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D36" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A36,'Test Cases'!H2:H134,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A36,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E36" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A36,'Test Cases'!H2:H134,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B146,A36,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F36" s="17">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
-        <v>631</v>
+        <v>670</v>
       </c>
       <c r="B37" s="17">
-        <f>COUNTIF('Test Cases'!B2:B134,A37)</f>
+        <f>COUNTIF('Test Cases'!B2:B146,A37)</f>
+        <v>4</v>
+      </c>
+      <c r="C37" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A37,'Test Cases'!H2:H146,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A37,'Test Cases'!H2:H146,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A37,'Test Cases'!H2:H146,"Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="B38" s="17">
+        <f>COUNTIF('Test Cases'!B2:B146,A38)</f>
         <v>5</v>
       </c>
-      <c r="C37" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A37,'Test Cases'!H2:H134,"Pass")</f>
+      <c r="C38" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A38,'Test Cases'!H2:H146,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="D37" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A37,'Test Cases'!H2:H134,"Fail")</f>
+      <c r="D38" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A38,'Test Cases'!H2:H146,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="17">
-        <f>COUNTIFS('Test Cases'!B2:B134,A37,'Test Cases'!H2:H134,"Blocked")</f>
+      <c r="E38" s="17">
+        <f>COUNTIFS('Test Cases'!B2:B146,A38,'Test Cases'!H2:H146,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F38" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
